--- a/AAII_Financials/Yearly/VRSN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VRSN_YR_FIN.xlsx
@@ -4693,7 +4693,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>215200</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
